--- a/event/templates/import_cont.xlsx
+++ b/event/templates/import_cont.xlsx
@@ -1,139 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/distr/attendly_ddev/event/templates/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880E3D2E-B9F8-E84D-A304-9CA665FDCD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="2060" yWindow="3280" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Import Contacts" sheetId="1" r:id="rId1"/>
+    <sheet name="Tablib Dataset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
-  <si>
-    <t>last_name</t>
-  </si>
-  <si>
-    <t>first_name</t>
-  </si>
-  <si>
-    <t>middle_name</t>
-  </si>
-  <si>
-    <t>company</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>type_guest</t>
-  </si>
-  <si>
-    <t>social_network_name</t>
-  </si>
-  <si>
-    <t>social_network_id</t>
-  </si>
-  <si>
-    <t>ВИП3</t>
-  </si>
-  <si>
-    <t>Сотрудник2</t>
-  </si>
-  <si>
-    <t>Иванов</t>
-  </si>
-  <si>
-    <t>Иван</t>
-  </si>
-  <si>
-    <t>Иванович</t>
-  </si>
-  <si>
-    <t>Вакуленко</t>
-  </si>
-  <si>
-    <t>Василий</t>
-  </si>
-  <si>
-    <t>basta</t>
-  </si>
-  <si>
-    <t>VK</t>
-  </si>
-  <si>
-    <t>ВИП</t>
-  </si>
-  <si>
-    <t>Сотрудник</t>
-  </si>
-  <si>
-    <t>Создаст контакт Иванов Иван Иванович</t>
-  </si>
-  <si>
-    <t>Создаст контакт Вакуленко Василий и добавит контакт инстаграм</t>
-  </si>
-  <si>
-    <t>Telegram</t>
-  </si>
-  <si>
-    <t>Instagram</t>
-  </si>
-  <si>
-    <t>Обновит контакт Вакуленко Василий и добавит контакт телеграм</t>
-  </si>
-  <si>
-    <t>VK Video</t>
-  </si>
-  <si>
-    <t>social_network_subscribers</t>
-  </si>
-  <si>
-    <t>producer</t>
-  </si>
-  <si>
-    <t>Фомичева</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -151,29 +49,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,150 +412,289 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="58.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>27</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>middle_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nickname</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>type_guest</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>producer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_1_name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_1_id</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_1_subscribers</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_2_name</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_2_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_2_subscribers</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_3_name</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_3_id</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>social_network_3_subscribers</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Иванов</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Иван</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Иванович</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ВИП</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Фомичева</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Создаст контакт Иванов Иван Иванович</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://vk.com/ivanov</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3">
-        <v>900</v>
-      </c>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Вакуленко</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Василий</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>basta</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ВИП3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Создаст/обновит контакт Вакуленко Василий, добавит соцсети</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://t.me/vakulenko</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://instagram.com/vakulenko</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>105400</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1234567890</v>
-      </c>
-      <c r="L4" s="3">
-        <v>500</v>
-      </c>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Петров</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Пётр</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MQP</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Сотрудник2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Мусор в поле соцсети будет очищен автоматически</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Сотрудник MQP</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/event/templates/import_cont.xlsx
+++ b/event/templates/import_cont.xlsx
@@ -417,196 +417,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="58" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Фамилия</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>middle_name</t>
+          <t>Имя</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>nickname</t>
+          <t>Отчество</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>Ник</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Компания</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>type_guest</t>
+          <t>Категория</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>producer</t>
+          <t>Тип гостя</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>Фамилия продюсера</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>social_network_1_name</t>
+          <t>Имя продюсера</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>social_network_1_id</t>
+          <t>Комментарий</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>social_network_1_subscribers</t>
+          <t>Соцсеть 1</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>social_network_2_name</t>
+          <t>Ссылка 1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>social_network_2_id</t>
+          <t>Подписчики 1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>social_network_2_subscribers</t>
+          <t>Соцсеть 2</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>social_network_3_name</t>
+          <t>Ссылка 2</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>social_network_3_id</t>
+          <t>Подписчики 2</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>social_network_3_subscribers</t>
+          <t>Соцсеть 3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка 3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Подписчики 3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Иванов</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Иванович</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>ВИП</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Сотрудник</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Фомичева</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Линда</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Создаст контакт Иванов Иван Иванович</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>VK</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://vk.com/ivanov</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>15000</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Вакуленко</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Василий</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>basta</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -615,86 +609,68 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Создаст/обновит контакт Вакуленко Василий, добавит соцсети</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://t.me/vakulenko</t>
+          <t>Обновит категорию у карточки #1 по ID, остальные поля не тронет</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>https://instagram.com/vakulenko</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>105400</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Петров</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Пётр</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MQP</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Сотрудник2</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Гость</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Мусор в поле соцсети будет очищен автоматически</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>VK</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Сотрудник MQP</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/event/templates/import_cont.xlsx
+++ b/event/templates/import_cont.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,45 +478,55 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Наименование события</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Соцсеть 1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ссылка 1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Подписчики 1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Соцсеть 2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Ссылка 2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Подписчики 2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Соцсеть 3</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ссылка 3</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Подписчики 3</t>
         </is>
@@ -568,27 +578,41 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>ТУСА 3.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Зарегистрирован</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>VK</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://vk.com/ivanov</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -625,6 +649,8 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -656,21 +682,27 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>ТУСА 3.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>VK</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Сотрудник MQP</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/event/templates/import_cont.xlsx
+++ b/event/templates/import_cont.xlsx
@@ -417,214 +417,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Фамилия</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Имя</t>
+          <t>middle_name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Отчество</t>
+          <t>nickname</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ник</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Компания</t>
+          <t>category</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Категория</t>
+          <t>type_guest</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Тип гостя</t>
+          <t>producer</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Фамилия продюсера</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Имя продюсера</t>
+          <t>social_network_name</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Комментарий</t>
+          <t>social_network_id</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Наименование события</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Соцсеть 1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Ссылка 1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Подписчики 1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Соцсеть 2</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Ссылка 2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Подписчики 2</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Соцсеть 3</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Ссылка 3</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Подписчики 3</t>
+          <t>social_network_subscribers</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Иванов</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Иванов</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Иванович</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Иванович</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Мария Валова</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Личный</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ВИП</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ВИП</t>
+          <t>Инфлюенсер</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Сотрудник</t>
+          <t>Бубнова</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Фомичева</t>
+          <t>Создаст контакт Иванов Иван Иванович</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Линда</t>
+          <t>VK</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Создаст контакт Иванов Иван Иванович</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>ТУСА 3.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Зарегистрирован</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>VK</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
           <t>https://vk.com/ivanov</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>15000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Вакуленко</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Вакуленко</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>Василий</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>basta</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -633,76 +567,22 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Создаст/обновит контакт Вакуленко Василий, добавит контакт инстаграм</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Обновит категорию у карточки #1 по ID, остальные поля не тронет</t>
+          <t>https://www.instagram.com/vakulenko</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Петров</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Пётр</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Гость</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Мусор в поле соцсети будет очищен автоматически</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ТУСА 3.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>VK</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Сотрудник MQP</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
